--- a/results/MC_Dist=Exp_n=500_LT=0.3_C=0.2_B=100.xlsx
+++ b/results/MC_Dist=Exp_n=500_LT=0.3_C=0.2_B=100.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -120,13 +120,16 @@
     <t xml:space="preserve">Gamma</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5,1</t>
+    <t xml:space="preserve">1,0.8</t>
   </si>
   <si>
     <t xml:space="preserve">x1.mean</t>
   </si>
   <si>
     <t xml:space="preserve">x1.sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8</t>
   </si>
   <si>
     <t xml:space="preserve">x2.mean</t>
@@ -542,19 +545,19 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.03168309763757</v>
+        <v>-1.01707217492343</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0316830976375697</v>
+        <v>-0.0170721749234342</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0148319792288236</v>
+        <v>0.0126274184990817</v>
       </c>
       <c r="E2" t="n">
-        <v>0.118185612247579</v>
+        <v>0.111626900845581</v>
       </c>
       <c r="F2" t="n">
-        <v>0.94</v>
+        <v>0.96</v>
       </c>
       <c r="G2" t="n">
         <v>0.99</v>
@@ -565,22 +568,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.977751341047119</v>
+        <v>-0.959343258043999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0222486589528814</v>
+        <v>0.0406567419560008</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0120576184996399</v>
+        <v>0.0135991680623969</v>
       </c>
       <c r="E3" t="n">
-        <v>0.108071317990297</v>
+        <v>0.10984928791979</v>
       </c>
       <c r="F3" t="n">
-        <v>0.93</v>
+        <v>0.94</v>
       </c>
       <c r="G3" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="4">
@@ -588,22 +591,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>1.50297821283227</v>
+        <v>1.00046106825374</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00297821283226996</v>
+        <v>0.000461068253737817</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0177487887496675</v>
+        <v>0.0198447423402866</v>
       </c>
       <c r="E4" t="n">
-        <v>0.133862280344326</v>
+        <v>0.141580293656535</v>
       </c>
       <c r="F4" t="n">
-        <v>0.97</v>
+        <v>0.94</v>
       </c>
       <c r="G4" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="5">
@@ -611,22 +614,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>1.21459343911601</v>
+        <v>0.963620595695433</v>
       </c>
       <c r="C5" t="n">
-        <v>0.214593439116005</v>
+        <v>0.163620595695433</v>
       </c>
       <c r="D5" t="n">
-        <v>0.10599245046082</v>
+        <v>0.0655918260731527</v>
       </c>
       <c r="E5" t="n">
-        <v>0.246064183031366</v>
+        <v>0.198020830292476</v>
       </c>
       <c r="F5" t="n">
         <v>0.82</v>
       </c>
       <c r="G5" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="6">
@@ -634,22 +637,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>2.04545848976493</v>
+        <v>2.01560913163874</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0454584897649282</v>
+        <v>0.0156091316387399</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00560978115624277</v>
+        <v>0.00317524803209661</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0598255617856145</v>
+        <v>0.054417048739492</v>
       </c>
       <c r="F6" t="n">
-        <v>0.88</v>
+        <v>0.94</v>
       </c>
       <c r="G6" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -780,20 +783,20 @@
         <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
@@ -812,2325 +815,2325 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-1.2172702358591</v>
+        <v>-0.932399495744613</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.07521897589127</v>
+        <v>-0.834608119760708</v>
       </c>
       <c r="C2" t="n">
-        <v>1.67993814288853</v>
+        <v>0.846592538234216</v>
       </c>
       <c r="D2" t="n">
-        <v>1.48794683487123</v>
+        <v>0.9199144335734</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.955190911374802</v>
+        <v>-1.17801980071196</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.19299002457059</v>
+        <v>-1.58867246301968</v>
       </c>
       <c r="G2" t="n">
-        <v>2.09216242832931</v>
+        <v>2.02236215535767</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-1.07130027111315</v>
+        <v>-0.928880487384547</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.826659881986931</v>
+        <v>-0.948389443925024</v>
       </c>
       <c r="C3" t="n">
-        <v>1.29459466102624</v>
+        <v>0.884431963238555</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3191809864356</v>
+        <v>0.546345539691226</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.886746835478032</v>
+        <v>-0.97068247474778</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.312644795613</v>
+        <v>-1.48890546686732</v>
       </c>
       <c r="G3" t="n">
-        <v>2.07971369128701</v>
+        <v>1.92158737344877</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0.982250724614528</v>
+        <v>-1.12325981985974</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.893931299924071</v>
+        <v>-1.01006126378405</v>
       </c>
       <c r="C4" t="n">
-        <v>1.42602101986576</v>
+        <v>1.04229242815921</v>
       </c>
       <c r="D4" t="n">
-        <v>1.19960391820421</v>
+        <v>1.1576344835518</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.96404504283033</v>
+        <v>-1.04527200735942</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.57653134506724</v>
+        <v>-1.4368744630008</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0603769678074</v>
+        <v>1.99563957493462</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-1.05150477307355</v>
+        <v>-1.21613694950253</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.780292242642568</v>
+        <v>-1.01835894330013</v>
       </c>
       <c r="C5" t="n">
-        <v>1.44831303173034</v>
+        <v>1.06083695577923</v>
       </c>
       <c r="D5" t="n">
-        <v>1.26615785000055</v>
+        <v>1.31321201721771</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.909694874965422</v>
+        <v>-0.827545624562798</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.43749634445325</v>
+        <v>-1.17324908358264</v>
       </c>
       <c r="G5" t="n">
-        <v>2.09578451653648</v>
+        <v>2.01330945693302</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-1.22498049698212</v>
+        <v>-1.08481237541452</v>
       </c>
       <c r="B6" t="n">
-        <v>-1.03293722531332</v>
+        <v>-0.909765086253226</v>
       </c>
       <c r="C6" t="n">
-        <v>1.55092493590654</v>
+        <v>0.924567886221818</v>
       </c>
       <c r="D6" t="n">
-        <v>1.57290013337837</v>
+        <v>1.21803996803193</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.75175993600278</v>
+        <v>-1.19280001143982</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.23243818509508</v>
+        <v>-1.46122813357288</v>
       </c>
       <c r="G6" t="n">
-        <v>1.98000363724475</v>
+        <v>2.11757266820152</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0.877216094181979</v>
+        <v>-1.16517047451082</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.988279836935681</v>
+        <v>-0.949432425995911</v>
       </c>
       <c r="C7" t="n">
-        <v>1.53058982645597</v>
+        <v>0.974873492763851</v>
       </c>
       <c r="D7" t="n">
-        <v>1.04145657162211</v>
+        <v>1.11557146533614</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.08046363802669</v>
+        <v>-0.949906932337697</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.68555567519377</v>
+        <v>-1.28151505182467</v>
       </c>
       <c r="G7" t="n">
-        <v>2.00413814732589</v>
+        <v>1.89969991856911</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0.885557245081219</v>
+        <v>-0.869505581703126</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.917944635670286</v>
+        <v>-1.21278062469278</v>
       </c>
       <c r="C8" t="n">
-        <v>1.44191857864491</v>
+        <v>1.19304842864298</v>
       </c>
       <c r="D8" t="n">
-        <v>0.916879748023525</v>
+        <v>0.572970329027018</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.15578646458689</v>
+        <v>-1.04024742826985</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.62035118232075</v>
+        <v>-1.48351085514876</v>
       </c>
       <c r="G8" t="n">
-        <v>2.09790183682784</v>
+        <v>1.94468066382362</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-1.07219893022085</v>
+        <v>-1.10121584540096</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.00435774069118</v>
+        <v>-0.862210842191897</v>
       </c>
       <c r="C9" t="n">
-        <v>1.54326888143596</v>
+        <v>0.9056308902628</v>
       </c>
       <c r="D9" t="n">
-        <v>1.41331382577946</v>
+        <v>1.20359186554133</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.946997609200601</v>
+        <v>-1.04214921265531</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.43255164304016</v>
+        <v>-1.44637734765254</v>
       </c>
       <c r="G9" t="n">
-        <v>2.02719964852798</v>
+        <v>2.01726956088856</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-1.02420326568886</v>
+        <v>-0.993481466851333</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.992238373830264</v>
+        <v>-0.99204770505805</v>
       </c>
       <c r="C10" t="n">
-        <v>1.49074575380768</v>
+        <v>1.04728833170084</v>
       </c>
       <c r="D10" t="n">
-        <v>1.23074153267868</v>
+        <v>0.787772942663033</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.87942166657156</v>
+        <v>-0.909357002514372</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.50070545633742</v>
+        <v>-1.35752640919216</v>
       </c>
       <c r="G10" t="n">
-        <v>2.08015203077406</v>
+        <v>2.10560849728819</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-1.20958048245378</v>
+        <v>-0.993441993322777</v>
       </c>
       <c r="B11" t="n">
-        <v>-1.23659454883661</v>
+        <v>-0.83242199179245</v>
       </c>
       <c r="C11" t="n">
-        <v>1.75306352796939</v>
+        <v>0.799627550464115</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5505627024732</v>
+        <v>0.835740273778297</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.933373701714182</v>
+        <v>-0.759481835240816</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.09916249151889</v>
+        <v>-1.42816042692712</v>
       </c>
       <c r="G11" t="n">
-        <v>1.9802449537946</v>
+        <v>2.00935933720301</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-1.11914034501343</v>
+        <v>-0.960811007578711</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.983616491165215</v>
+        <v>-0.997070471380294</v>
       </c>
       <c r="C12" t="n">
-        <v>1.29308784946656</v>
+        <v>0.991969277166451</v>
       </c>
       <c r="D12" t="n">
-        <v>1.40732137870757</v>
+        <v>0.751357740768821</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.05087432009187</v>
+        <v>-1.05845432210675</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.38142411268641</v>
+        <v>-2.18870193220831</v>
       </c>
       <c r="G12" t="n">
-        <v>2.05352062719315</v>
+        <v>2.06556436194951</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-1.010451771676</v>
+        <v>-1.20053536199666</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.00997703432793</v>
+        <v>-1.03228342279487</v>
       </c>
       <c r="C13" t="n">
-        <v>1.42208820939792</v>
+        <v>1.2060114515745</v>
       </c>
       <c r="D13" t="n">
-        <v>1.26294614010359</v>
+        <v>1.05685394326903</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.09832445506984</v>
+        <v>-0.428173446835166</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.58476726339315</v>
+        <v>-1.07994538045017</v>
       </c>
       <c r="G13" t="n">
-        <v>1.99639324752675</v>
+        <v>2.09336372962505</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-1.14183028497566</v>
+        <v>-0.868674158886741</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.01721743834697</v>
+        <v>-0.969835915253441</v>
       </c>
       <c r="C14" t="n">
-        <v>1.55088861138318</v>
+        <v>1.0369327385494</v>
       </c>
       <c r="D14" t="n">
-        <v>1.36132279152524</v>
+        <v>0.690757554386818</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.03347562366047</v>
+        <v>-1.22589487121157</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.31461183728669</v>
+        <v>-1.60236123622358</v>
       </c>
       <c r="G14" t="n">
-        <v>1.99577959844645</v>
+        <v>2.11239837008848</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-1.07075117232009</v>
+        <v>-0.988377594235285</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.929745691190963</v>
+        <v>-1.10233167384911</v>
       </c>
       <c r="C15" t="n">
-        <v>1.35523685385843</v>
+        <v>1.20600229935101</v>
       </c>
       <c r="D15" t="n">
-        <v>1.33674952300121</v>
+        <v>1.00216678833032</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.19729399279411</v>
+        <v>-1.28292847632653</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.25434238594076</v>
+        <v>-1.51518780677878</v>
       </c>
       <c r="G15" t="n">
-        <v>2.05272448039682</v>
+        <v>1.99298401532502</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-0.9824027573519</v>
+        <v>-0.863912899846096</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.850286768517126</v>
+        <v>-0.941423080539284</v>
       </c>
       <c r="C16" t="n">
-        <v>1.38202106003941</v>
+        <v>0.980108928079074</v>
       </c>
       <c r="D16" t="n">
-        <v>1.17811476233607</v>
+        <v>0.716264084954386</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.13934894649282</v>
+        <v>-1.2938440234613</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5558293225895</v>
+        <v>-1.65695159133477</v>
       </c>
       <c r="G16" t="n">
-        <v>2.06339930319316</v>
+        <v>1.92144665596455</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-1.37039504429927</v>
+        <v>-1.04964082421038</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.978634771254244</v>
+        <v>-0.998847414966932</v>
       </c>
       <c r="C17" t="n">
-        <v>1.66009455532763</v>
+        <v>1.08152605812906</v>
       </c>
       <c r="D17" t="n">
-        <v>1.78999104570596</v>
+        <v>0.994714722345322</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.814341281988136</v>
+        <v>-1.03819662681346</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.70295149183504</v>
+        <v>-1.44802531661895</v>
       </c>
       <c r="G17" t="n">
-        <v>2.01701978976124</v>
+        <v>2.0176415483287</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-0.825762055335972</v>
+        <v>-0.870011967644369</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.926908722699739</v>
+        <v>-1.03914860569577</v>
       </c>
       <c r="C18" t="n">
-        <v>1.4596070191843</v>
+        <v>1.13084616589499</v>
       </c>
       <c r="D18" t="n">
-        <v>0.90244725453274</v>
+        <v>0.500996305818472</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.40616064539747</v>
+        <v>-1.14062443557875</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.73622360037812</v>
+        <v>-1.59635430029159</v>
       </c>
       <c r="G18" t="n">
-        <v>1.96913736217155</v>
+        <v>2.09525007881432</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-0.990467880267817</v>
+        <v>-1.07563792659142</v>
       </c>
       <c r="B19" t="n">
-        <v>-1.04523831841157</v>
+        <v>-0.877045368954683</v>
       </c>
       <c r="C19" t="n">
-        <v>1.65812412172666</v>
+        <v>0.899467936593912</v>
       </c>
       <c r="D19" t="n">
-        <v>0.907128988096552</v>
+        <v>1.21761774701369</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.09076848262259</v>
+        <v>-1.1530341121408</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.06595622306163</v>
+        <v>-1.48220577049653</v>
       </c>
       <c r="G19" t="n">
-        <v>2.10804790410805</v>
+        <v>2.02439232925004</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-1.07411926534074</v>
+        <v>-1.14073880812657</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.878192875033744</v>
+        <v>-1.35914424817448</v>
       </c>
       <c r="C20" t="n">
-        <v>1.38062780115608</v>
+        <v>1.41585813761755</v>
       </c>
       <c r="D20" t="n">
-        <v>1.36145327649907</v>
+        <v>0.990961620037719</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.827186633686426</v>
+        <v>-0.858446932852564</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.39843331468314</v>
+        <v>-1.8602664190769</v>
       </c>
       <c r="G20" t="n">
-        <v>2.16832802969651</v>
+        <v>2.00823634201957</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-1.00855901740789</v>
+        <v>-0.911798858764951</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.843357585028356</v>
+        <v>-1.02388568222662</v>
       </c>
       <c r="C21" t="n">
-        <v>1.29260376124683</v>
+        <v>1.13822265232497</v>
       </c>
       <c r="D21" t="n">
-        <v>1.36556956580153</v>
+        <v>0.643101616791487</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.957929717477557</v>
+        <v>-0.951173226682064</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.50017114116637</v>
+        <v>-1.47741478065361</v>
       </c>
       <c r="G21" t="n">
-        <v>2.09600827554816</v>
+        <v>1.93312571989798</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-0.956480988189927</v>
+        <v>-1.05237354838769</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.989585697687797</v>
+        <v>-0.910943060484259</v>
       </c>
       <c r="C22" t="n">
-        <v>1.49993424849359</v>
+        <v>1.10333523213215</v>
       </c>
       <c r="D22" t="n">
-        <v>1.08775185772442</v>
+        <v>0.985896168679237</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.980802575784459</v>
+        <v>-0.996579962762347</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.56434826251373</v>
+        <v>-1.32713322335796</v>
       </c>
       <c r="G22" t="n">
-        <v>2.03867706814433</v>
+        <v>2.08896664798068</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-0.819340734945487</v>
+        <v>-1.07539945702399</v>
       </c>
       <c r="B23" t="n">
-        <v>-1.0198896808093</v>
+        <v>-0.995931278538175</v>
       </c>
       <c r="C23" t="n">
-        <v>1.4565878816134</v>
+        <v>1.10373656402336</v>
       </c>
       <c r="D23" t="n">
-        <v>0.75301294083958</v>
+        <v>0.945622952395169</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.40526152070821</v>
+        <v>-0.884929385494492</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.55828885782943</v>
+        <v>-1.37235517344526</v>
       </c>
       <c r="G23" t="n">
-        <v>2.05324387105577</v>
+        <v>1.94797549374739</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-1.05748838966898</v>
+        <v>-1.06270599394077</v>
       </c>
       <c r="B24" t="n">
-        <v>-1.00558912985838</v>
+        <v>-1.00185932285413</v>
       </c>
       <c r="C24" t="n">
-        <v>1.55726350494981</v>
+        <v>0.96755837425628</v>
       </c>
       <c r="D24" t="n">
-        <v>1.30804894871835</v>
+        <v>0.832485217617884</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.08225680107167</v>
+        <v>-0.615388737620073</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.52127221085151</v>
+        <v>-1.27366783065631</v>
       </c>
       <c r="G24" t="n">
-        <v>1.99609661762143</v>
+        <v>1.99333644415205</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-0.996252014611537</v>
+        <v>-1.09536917250134</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.900414888115457</v>
+        <v>-0.920247896201994</v>
       </c>
       <c r="C25" t="n">
-        <v>1.51487746154406</v>
+        <v>1.1163982882492</v>
       </c>
       <c r="D25" t="n">
-        <v>1.0453234298214</v>
+        <v>0.990037136738852</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.815322323365303</v>
+        <v>-1.08715953064245</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.48055297376366</v>
+        <v>-2.12783855382819</v>
       </c>
       <c r="G25" t="n">
-        <v>2.09505309149565</v>
+        <v>2.05368965524852</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-1.1002449810226</v>
+        <v>-0.91912427866797</v>
       </c>
       <c r="B26" t="n">
-        <v>-1.00491945181569</v>
+        <v>-1.00302920634944</v>
       </c>
       <c r="C26" t="n">
-        <v>1.68584731935617</v>
+        <v>1.19764514197089</v>
       </c>
       <c r="D26" t="n">
-        <v>1.16997261038477</v>
+        <v>0.828684875538551</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.964486334526762</v>
+        <v>-1.39439975638539</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.93523608199053</v>
+        <v>-2.38806918937329</v>
       </c>
       <c r="G26" t="n">
-        <v>2.12204587583082</v>
+        <v>2.01079514024915</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-1.08935752048356</v>
+        <v>-1.19085938503094</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.846443057202382</v>
+        <v>-0.760460839224806</v>
       </c>
       <c r="C27" t="n">
-        <v>1.45718747506488</v>
+        <v>0.798310691852301</v>
       </c>
       <c r="D27" t="n">
-        <v>1.32672720210511</v>
+        <v>1.20761744672892</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.05213611624682</v>
+        <v>-0.844555811370407</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.32590671993963</v>
+        <v>-1.26206766200312</v>
       </c>
       <c r="G27" t="n">
-        <v>2.0391804170343</v>
+        <v>2.02270803869393</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-0.923976885467337</v>
+        <v>-0.967903628351781</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.885277058172135</v>
+        <v>-0.905512469757138</v>
       </c>
       <c r="C28" t="n">
-        <v>1.42560593233339</v>
+        <v>0.91403276897389</v>
       </c>
       <c r="D28" t="n">
-        <v>1.1200410952862</v>
+        <v>0.92543400001077</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.06749561153824</v>
+        <v>-1.19876636504315</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.63121476131942</v>
+        <v>-1.61236019014646</v>
       </c>
       <c r="G28" t="n">
-        <v>2.00796864288398</v>
+        <v>2.12252905554218</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>-1.21200052431255</v>
+        <v>-0.969282732655178</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.92999427365009</v>
+        <v>-0.963520663054115</v>
       </c>
       <c r="C29" t="n">
-        <v>1.41063556491166</v>
+        <v>0.975368308431573</v>
       </c>
       <c r="D29" t="n">
-        <v>1.7110752082649</v>
+        <v>0.857744851485171</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.674610620593885</v>
+        <v>-1.07302479153381</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.34895762188978</v>
+        <v>-1.47030283511486</v>
       </c>
       <c r="G29" t="n">
-        <v>2.02855838174036</v>
+        <v>1.97456057475366</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-1.1947997450963</v>
+        <v>-1.01213211099664</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.930170448149108</v>
+        <v>-1.10846652974922</v>
       </c>
       <c r="C30" t="n">
-        <v>1.53793016364329</v>
+        <v>1.03103610876122</v>
       </c>
       <c r="D30" t="n">
-        <v>1.54557025235674</v>
+        <v>1.04185353840184</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.794380352473683</v>
+        <v>-1.11381937604385</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.19367453536973</v>
+        <v>-1.50768789815965</v>
       </c>
       <c r="G30" t="n">
-        <v>2.10170606569984</v>
+        <v>2.00504555052984</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-0.90592441790134</v>
+        <v>-0.961415016896362</v>
       </c>
       <c r="B31" t="n">
-        <v>-1.09708893668461</v>
+        <v>-0.792204714501345</v>
       </c>
       <c r="C31" t="n">
-        <v>1.65281005156343</v>
+        <v>0.79536690740183</v>
       </c>
       <c r="D31" t="n">
-        <v>0.910353072693029</v>
+        <v>1.02597674618492</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.91216066171957</v>
+        <v>-1.07302332829885</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.51842687445278</v>
+        <v>-1.48306743114833</v>
       </c>
       <c r="G31" t="n">
-        <v>2.02678386968692</v>
+        <v>2.0700476524244</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-0.825650776742206</v>
+        <v>-1.0438101065093</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.874292196846243</v>
+        <v>-0.701979337745367</v>
       </c>
       <c r="C32" t="n">
-        <v>1.4241523274799</v>
+        <v>0.779994975385685</v>
       </c>
       <c r="D32" t="n">
-        <v>1.02934802861045</v>
+        <v>1.06764930854585</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.25932534712101</v>
+        <v>-0.873738924161304</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.68780316163239</v>
+        <v>-1.37582131038369</v>
       </c>
       <c r="G32" t="n">
-        <v>2.19598502853393</v>
+        <v>2.11599695886604</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-1.28586506365427</v>
+        <v>-1.06339388094697</v>
       </c>
       <c r="B33" t="n">
-        <v>-1.07790236238346</v>
+        <v>-1.22975359680798</v>
       </c>
       <c r="C33" t="n">
-        <v>1.63961661864082</v>
+        <v>1.31969844088877</v>
       </c>
       <c r="D33" t="n">
-        <v>1.61206217088794</v>
+        <v>0.917227763566492</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.465594702154838</v>
+        <v>-0.956060194555943</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.13704812073259</v>
+        <v>-1.39965340316782</v>
       </c>
       <c r="G33" t="n">
-        <v>2.04319445331224</v>
+        <v>1.9951426116877</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>-1.23783227857784</v>
+        <v>-1.04632780062034</v>
       </c>
       <c r="B34" t="n">
-        <v>-1.13448391247088</v>
+        <v>-0.957716346514119</v>
       </c>
       <c r="C34" t="n">
-        <v>1.60385116648497</v>
+        <v>1.01942747957345</v>
       </c>
       <c r="D34" t="n">
-        <v>1.61833202898877</v>
+        <v>1.05638489194907</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.713335108374568</v>
+        <v>-1.15281125316041</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.26046034961128</v>
+        <v>-1.48800039407158</v>
       </c>
       <c r="G34" t="n">
-        <v>1.97402613175097</v>
+        <v>1.98478049874998</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-0.87049269276369</v>
+        <v>-0.950476116309803</v>
       </c>
       <c r="B35" t="n">
-        <v>-1.00379644969527</v>
+        <v>-1.14031513167192</v>
       </c>
       <c r="C35" t="n">
-        <v>1.40811364504683</v>
+        <v>1.22572299853021</v>
       </c>
       <c r="D35" t="n">
-        <v>0.942360211912997</v>
+        <v>1.02700941584605</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.29777608142992</v>
+        <v>-1.14267555514614</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.62150782315373</v>
+        <v>-1.5477193862787</v>
       </c>
       <c r="G35" t="n">
-        <v>1.98059618033202</v>
+        <v>1.94242170633855</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>-1.11704980397899</v>
+        <v>-0.88333817640861</v>
       </c>
       <c r="B36" t="n">
-        <v>-0.97334243974072</v>
+        <v>-0.952299861718601</v>
       </c>
       <c r="C36" t="n">
-        <v>1.67614623252134</v>
+        <v>1.00982115490305</v>
       </c>
       <c r="D36" t="n">
-        <v>1.52243660961774</v>
+        <v>0.926871106520951</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.928075944372337</v>
+        <v>-1.41010397382782</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.42002231963525</v>
+        <v>-1.69418745604643</v>
       </c>
       <c r="G36" t="n">
-        <v>2.04625597836216</v>
+        <v>1.95592759856031</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-1.08543083614105</v>
+        <v>-0.891934907871246</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.944868894524089</v>
+        <v>-0.927150329667189</v>
       </c>
       <c r="C37" t="n">
-        <v>1.43583123294188</v>
+        <v>0.818887409608944</v>
       </c>
       <c r="D37" t="n">
-        <v>1.39517398639383</v>
+        <v>0.801038576981378</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.838225489930725</v>
+        <v>-1.29771779143851</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.24876019018179</v>
+        <v>-1.75736520396122</v>
       </c>
       <c r="G37" t="n">
-        <v>2.10714696855497</v>
+        <v>1.9324740943243</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-1.05128384115938</v>
+        <v>-0.964991894645874</v>
       </c>
       <c r="B38" t="n">
-        <v>-1.06559838711825</v>
+        <v>-0.826188444388664</v>
       </c>
       <c r="C38" t="n">
-        <v>1.67129464093149</v>
+        <v>0.82379796901474</v>
       </c>
       <c r="D38" t="n">
-        <v>1.18649467983383</v>
+        <v>0.949347266261883</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.919123521052296</v>
+        <v>-1.39672737520515</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.38596131360558</v>
+        <v>-1.59131627263536</v>
       </c>
       <c r="G38" t="n">
-        <v>2.02562275657138</v>
+        <v>2.09839615521688</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-1.01779197901561</v>
+        <v>-0.948551723951334</v>
       </c>
       <c r="B39" t="n">
-        <v>-1.00318379005615</v>
+        <v>-1.0605072699743</v>
       </c>
       <c r="C39" t="n">
-        <v>1.5261158219512</v>
+        <v>1.07321978024199</v>
       </c>
       <c r="D39" t="n">
-        <v>1.1373844069029</v>
+        <v>0.839298840557779</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.11784585427734</v>
+        <v>-1.27573247352494</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.394347818505</v>
+        <v>-2.38241695680478</v>
       </c>
       <c r="G39" t="n">
-        <v>1.95576738644745</v>
+        <v>1.9839838936399</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>-0.864567494642541</v>
+        <v>-1.03764315010553</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.674794384485653</v>
+        <v>-1.03927999979316</v>
       </c>
       <c r="C40" t="n">
-        <v>1.31543766809248</v>
+        <v>1.00963077613714</v>
       </c>
       <c r="D40" t="n">
-        <v>1.0132183750869</v>
+        <v>1.03760505351181</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.184812065084</v>
+        <v>-1.18415109251059</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.70586139052339</v>
+        <v>-1.45696972493496</v>
       </c>
       <c r="G40" t="n">
-        <v>2.14276726398308</v>
+        <v>2.00450432147374</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-1.13966569576237</v>
+        <v>-0.950868837937011</v>
       </c>
       <c r="B41" t="n">
-        <v>-1.10181816656211</v>
+        <v>-1.25747000869996</v>
       </c>
       <c r="C41" t="n">
-        <v>1.6789314409</v>
+        <v>1.28984971066394</v>
       </c>
       <c r="D41" t="n">
-        <v>1.38504774190823</v>
+        <v>0.747302314566612</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.868859440223203</v>
+        <v>-0.937219026646057</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.29951814340019</v>
+        <v>-1.40843331910187</v>
       </c>
       <c r="G41" t="n">
-        <v>2.04496007960811</v>
+        <v>1.95804553002766</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>-1.0529169283617</v>
+        <v>-1.11973148546963</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.747547731730864</v>
+        <v>-0.869219667736123</v>
       </c>
       <c r="C42" t="n">
-        <v>1.24141791719119</v>
+        <v>0.99920012146074</v>
       </c>
       <c r="D42" t="n">
-        <v>1.37564723030965</v>
+        <v>1.03389347125125</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.984115672304757</v>
+        <v>-0.756297517746853</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.44538658925725</v>
+        <v>-1.2603248810033</v>
       </c>
       <c r="G42" t="n">
-        <v>2.12327487025259</v>
+        <v>1.99510961098648</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>-0.982869662656579</v>
+        <v>-0.980231649737779</v>
       </c>
       <c r="B43" t="n">
-        <v>-0.838531737442959</v>
+        <v>-1.09884799770114</v>
       </c>
       <c r="C43" t="n">
-        <v>1.30044179239813</v>
+        <v>1.17331739395941</v>
       </c>
       <c r="D43" t="n">
-        <v>1.10139259274406</v>
+        <v>0.800298192509102</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.11994464421419</v>
+        <v>-1.23705006748327</v>
       </c>
       <c r="F43" t="n">
-        <v>-1.5469818716348</v>
+        <v>-1.55142289272168</v>
       </c>
       <c r="G43" t="n">
-        <v>2.07732000686846</v>
+        <v>1.93292999052387</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>-1.04152578547344</v>
+        <v>-1.03089202980546</v>
       </c>
       <c r="B44" t="n">
-        <v>-1.01873399076734</v>
+        <v>-0.973449888664434</v>
       </c>
       <c r="C44" t="n">
-        <v>1.54731790190526</v>
+        <v>1.11880616504764</v>
       </c>
       <c r="D44" t="n">
-        <v>1.07612137490311</v>
+        <v>1.0166404416641</v>
       </c>
       <c r="E44" t="n">
-        <v>-1.12820219563907</v>
+        <v>-0.998068685830399</v>
       </c>
       <c r="F44" t="n">
-        <v>-2.0992384448637</v>
+        <v>-1.41588532309662</v>
       </c>
       <c r="G44" t="n">
-        <v>2.04894269655942</v>
+        <v>1.97050737486397</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>-0.938204623935149</v>
+        <v>-1.14677578604517</v>
       </c>
       <c r="B45" t="n">
-        <v>-0.74423291783997</v>
+        <v>-1.00560647823778</v>
       </c>
       <c r="C45" t="n">
-        <v>1.18126536911147</v>
+        <v>1.05814215055212</v>
       </c>
       <c r="D45" t="n">
-        <v>1.1193695508535</v>
+        <v>1.24235611316226</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.987190480352552</v>
+        <v>-0.824943955065214</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.63930254394283</v>
+        <v>-1.39081594484308</v>
       </c>
       <c r="G45" t="n">
-        <v>2.05329565600638</v>
+        <v>2.02642755212964</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-1.11828940978937</v>
+        <v>-0.741500895430951</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.995452510064228</v>
+        <v>-1.02319638281024</v>
       </c>
       <c r="C46" t="n">
-        <v>1.39789396622878</v>
+        <v>1.31560874213999</v>
       </c>
       <c r="D46" t="n">
-        <v>1.37520153543872</v>
+        <v>0.522138099990007</v>
       </c>
       <c r="E46" t="n">
-        <v>-1.18432742412505</v>
+        <v>-1.42755744896221</v>
       </c>
       <c r="F46" t="n">
-        <v>-2.37436445706246</v>
+        <v>-1.77522762710678</v>
       </c>
       <c r="G46" t="n">
-        <v>1.89043410262019</v>
+        <v>2.13733590175254</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>-1.01506830428472</v>
+        <v>-1.16045231565385</v>
       </c>
       <c r="B47" t="n">
-        <v>-1.15236402852791</v>
+        <v>-0.951535078534523</v>
       </c>
       <c r="C47" t="n">
-        <v>1.69997221321134</v>
+        <v>1.01413079712184</v>
       </c>
       <c r="D47" t="n">
-        <v>1.11840745317043</v>
+        <v>1.19325978121646</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.09669662994373</v>
+        <v>-0.928616676830204</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.40454574025085</v>
+        <v>-1.34997194194579</v>
       </c>
       <c r="G47" t="n">
-        <v>2.03543834411746</v>
+        <v>2.02420706830397</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>-1.04310464922714</v>
+        <v>-1.12914927881171</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.949368421060113</v>
+        <v>-0.945298670135015</v>
       </c>
       <c r="C48" t="n">
-        <v>1.4789469828052</v>
+        <v>0.978682558440859</v>
       </c>
       <c r="D48" t="n">
-        <v>1.23000769796365</v>
+        <v>1.22566287824061</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.804209358576616</v>
+        <v>-0.96137784495249</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.32396471227231</v>
+        <v>-1.40280975955848</v>
       </c>
       <c r="G48" t="n">
-        <v>2.05446107117345</v>
+        <v>1.98992498485618</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>-0.922092090496554</v>
+        <v>-1.09463632553696</v>
       </c>
       <c r="B49" t="n">
-        <v>-1.01898326460437</v>
+        <v>-1.12516911997673</v>
       </c>
       <c r="C49" t="n">
-        <v>1.62730000187127</v>
+        <v>1.08523526440563</v>
       </c>
       <c r="D49" t="n">
-        <v>0.965254799361787</v>
+        <v>0.92601325665237</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.40691598881852</v>
+        <v>-0.896003406781817</v>
       </c>
       <c r="F49" t="n">
-        <v>-2.35279997808478</v>
+        <v>-1.16108525151152</v>
       </c>
       <c r="G49" t="n">
-        <v>2.06699182679937</v>
+        <v>2.02460206034745</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-0.872964445833518</v>
+        <v>-0.984685122392106</v>
       </c>
       <c r="B50" t="n">
-        <v>-0.909941099314722</v>
+        <v>-0.954330705898904</v>
       </c>
       <c r="C50" t="n">
-        <v>1.36111538443221</v>
+        <v>1.00750500401257</v>
       </c>
       <c r="D50" t="n">
-        <v>0.926993906262498</v>
+        <v>0.844248570053449</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.26246035450445</v>
+        <v>-1.04244517896477</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.61350011236616</v>
+        <v>-1.45179483795323</v>
       </c>
       <c r="G50" t="n">
-        <v>1.99699857349446</v>
+        <v>2.03300222700263</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>-0.99726468260592</v>
+        <v>-1.10107400931054</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.982653963655854</v>
+        <v>-0.928266451368335</v>
       </c>
       <c r="C51" t="n">
-        <v>1.53212489568654</v>
+        <v>0.929853942232243</v>
       </c>
       <c r="D51" t="n">
-        <v>1.0564465579016</v>
+        <v>0.965835758099897</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.904295105040381</v>
+        <v>-1.02698960819732</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.46630273527169</v>
+        <v>-1.28716370617916</v>
       </c>
       <c r="G51" t="n">
-        <v>2.02428841791083</v>
+        <v>1.96868004629561</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>-0.927816452847995</v>
+        <v>-0.994781154464341</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.940645773490252</v>
+        <v>-1.02603043290034</v>
       </c>
       <c r="C52" t="n">
-        <v>1.44826936680634</v>
+        <v>1.12856835467465</v>
       </c>
       <c r="D52" t="n">
-        <v>0.756382015545562</v>
+        <v>0.959926410565662</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.10009516002519</v>
+        <v>-0.849168293302271</v>
       </c>
       <c r="F52" t="n">
-        <v>-2.10177886803542</v>
+        <v>-1.43255934569559</v>
       </c>
       <c r="G52" t="n">
-        <v>1.9822674930584</v>
+        <v>2.02111383308642</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>-1.17602886525848</v>
+        <v>-1.0558919288465</v>
       </c>
       <c r="B53" t="n">
-        <v>-1.11276455520674</v>
+        <v>-1.06146106567905</v>
       </c>
       <c r="C53" t="n">
-        <v>1.64834604833946</v>
+        <v>1.09379169601192</v>
       </c>
       <c r="D53" t="n">
-        <v>1.49528837049568</v>
+        <v>1.12009288733289</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.807345640819268</v>
+        <v>-1.30279349594427</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.30588396829917</v>
+        <v>-1.47060547905633</v>
       </c>
       <c r="G53" t="n">
-        <v>1.9785410266512</v>
+        <v>2.00180696509013</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>-0.919715943543102</v>
+        <v>-1.0970269270069</v>
       </c>
       <c r="B54" t="n">
-        <v>-0.754844720013102</v>
+        <v>-1.12745518144885</v>
       </c>
       <c r="C54" t="n">
-        <v>1.37547395498435</v>
+        <v>1.18343692529289</v>
       </c>
       <c r="D54" t="n">
-        <v>0.93155165815281</v>
+        <v>0.920906155194436</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.08504218629757</v>
+        <v>-0.908036372934438</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.55605601990908</v>
+        <v>-1.26063964874499</v>
       </c>
       <c r="G54" t="n">
-        <v>2.1421439279727</v>
+        <v>2.04327018184062</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>-0.827138363815664</v>
+        <v>-0.843527900332888</v>
       </c>
       <c r="B55" t="n">
-        <v>-1.08978519121731</v>
+        <v>-0.964442745925394</v>
       </c>
       <c r="C55" t="n">
-        <v>1.52018585552997</v>
+        <v>0.955165251143592</v>
       </c>
       <c r="D55" t="n">
-        <v>0.749653483474679</v>
+        <v>0.626449335916605</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.45846046626678</v>
+        <v>-1.12163171374205</v>
       </c>
       <c r="F55" t="n">
-        <v>-2.45224668531064</v>
+        <v>-1.62418338150059</v>
       </c>
       <c r="G55" t="n">
-        <v>2.03537802706202</v>
+        <v>1.94197170253032</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>-1.08369519990981</v>
+        <v>-0.884019187994891</v>
       </c>
       <c r="B56" t="n">
-        <v>-1.11419284201882</v>
+        <v>-1.05775112601418</v>
       </c>
       <c r="C56" t="n">
-        <v>1.66775660529877</v>
+        <v>1.12240271114858</v>
       </c>
       <c r="D56" t="n">
-        <v>1.34564031842917</v>
+        <v>0.809588881623565</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.94638462742755</v>
+        <v>-1.30740476041431</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.42909049120537</v>
+        <v>-1.64163690197076</v>
       </c>
       <c r="G56" t="n">
-        <v>2.0101094446247</v>
+        <v>2.02638046280785</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>-1.00523295178082</v>
+        <v>-1.10082797923766</v>
       </c>
       <c r="B57" t="n">
-        <v>-0.947984649653319</v>
+        <v>-0.968903286905502</v>
       </c>
       <c r="C57" t="n">
-        <v>1.41779297563598</v>
+        <v>1.01306959566399</v>
       </c>
       <c r="D57" t="n">
-        <v>1.32447953242852</v>
+        <v>1.0588695602124</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.04178296015415</v>
+        <v>-0.748564929121288</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.50952464702283</v>
+        <v>-1.28394112852311</v>
       </c>
       <c r="G57" t="n">
-        <v>2.13443546952461</v>
+        <v>2.05036705686185</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>-1.05371538589823</v>
+        <v>-1.05608068326833</v>
       </c>
       <c r="B58" t="n">
-        <v>-1.12152779504799</v>
+        <v>-0.840551133156782</v>
       </c>
       <c r="C58" t="n">
-        <v>1.64414151606622</v>
+        <v>0.954653435149325</v>
       </c>
       <c r="D58" t="n">
-        <v>1.25662275474464</v>
+        <v>1.19625891271365</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.803596756955726</v>
+        <v>-1.23826927055232</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.40394083552219</v>
+        <v>-1.51614207868847</v>
       </c>
       <c r="G58" t="n">
-        <v>1.98647770127191</v>
+        <v>2.08234272047467</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>-1.03592608730407</v>
+        <v>-0.970411830081519</v>
       </c>
       <c r="B59" t="n">
-        <v>-0.936913464118562</v>
+        <v>-0.939192424846916</v>
       </c>
       <c r="C59" t="n">
-        <v>1.5095565421125</v>
+        <v>0.869102842813976</v>
       </c>
       <c r="D59" t="n">
-        <v>1.21063705590311</v>
+        <v>0.762576494474428</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.928728711477556</v>
+        <v>-0.671936287143508</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.47290388003539</v>
+        <v>-1.35718652884267</v>
       </c>
       <c r="G59" t="n">
-        <v>1.95898639678776</v>
+        <v>2.01983474037128</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>-1.01761944676714</v>
+        <v>-0.988686223929918</v>
       </c>
       <c r="B60" t="n">
-        <v>-1.05649317627843</v>
+        <v>-0.885123114963671</v>
       </c>
       <c r="C60" t="n">
-        <v>1.55551640782517</v>
+        <v>1.00238614480676</v>
       </c>
       <c r="D60" t="n">
-        <v>1.17162650776034</v>
+        <v>0.804760501063339</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.28232371275781</v>
+        <v>-1.07383698836011</v>
       </c>
       <c r="F60" t="n">
-        <v>-2.23855832330662</v>
+        <v>-1.39185222891246</v>
       </c>
       <c r="G60" t="n">
-        <v>1.96593478723293</v>
+        <v>2.0690487647472</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>-1.02257298158506</v>
+        <v>-1.19900161820547</v>
       </c>
       <c r="B61" t="n">
-        <v>-1.09029522973474</v>
+        <v>-0.849536020457597</v>
       </c>
       <c r="C61" t="n">
-        <v>1.52531935658669</v>
+        <v>0.807250258582788</v>
       </c>
       <c r="D61" t="n">
-        <v>0.820428025291134</v>
+        <v>1.0741291784814</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.969377285295222</v>
+        <v>-1.01101334922888</v>
       </c>
       <c r="F61" t="n">
-        <v>-2.02823707589777</v>
+        <v>-1.18087992106343</v>
       </c>
       <c r="G61" t="n">
-        <v>1.97677152636412</v>
+        <v>1.99832100187107</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>-1.18387134517873</v>
+        <v>-1.08328714099063</v>
       </c>
       <c r="B62" t="n">
-        <v>-0.953329366720068</v>
+        <v>-0.888251606176569</v>
       </c>
       <c r="C62" t="n">
-        <v>1.58755913554368</v>
+        <v>0.957939829207846</v>
       </c>
       <c r="D62" t="n">
-        <v>1.53334188540908</v>
+        <v>1.21930274994422</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.997129663335141</v>
+        <v>-0.847499786298447</v>
       </c>
       <c r="F62" t="n">
-        <v>-2.20753250095419</v>
+        <v>-1.33821116327957</v>
       </c>
       <c r="G62" t="n">
-        <v>2.056366179413</v>
+        <v>2.04229270056488</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>-0.902532844759392</v>
+        <v>-0.837331774208934</v>
       </c>
       <c r="B63" t="n">
-        <v>-0.895934585928578</v>
+        <v>-0.867419990363282</v>
       </c>
       <c r="C63" t="n">
-        <v>1.48598343769317</v>
+        <v>0.712309172894612</v>
       </c>
       <c r="D63" t="n">
-        <v>0.92974988632004</v>
+        <v>0.716728798948803</v>
       </c>
       <c r="E63" t="n">
-        <v>-1.37300447282972</v>
+        <v>-1.36444229998182</v>
       </c>
       <c r="F63" t="n">
-        <v>-2.34123562962627</v>
+        <v>-1.64481547031746</v>
       </c>
       <c r="G63" t="n">
-        <v>2.09615570239052</v>
+        <v>2.06375198475079</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>-1.01673995416892</v>
+        <v>-1.00829006294904</v>
       </c>
       <c r="B64" t="n">
-        <v>-1.01486812124541</v>
+        <v>-0.840035165928713</v>
       </c>
       <c r="C64" t="n">
-        <v>1.6796566687202</v>
+        <v>0.883591785126248</v>
       </c>
       <c r="D64" t="n">
-        <v>1.15197066233461</v>
+        <v>0.85931245344462</v>
       </c>
       <c r="E64" t="n">
-        <v>-1.11127209594222</v>
+        <v>-1.02444732182701</v>
       </c>
       <c r="F64" t="n">
-        <v>-2.04825638576501</v>
+        <v>-1.36296850541707</v>
       </c>
       <c r="G64" t="n">
-        <v>2.15068134923131</v>
+        <v>2.01181451236688</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>-0.959331150118847</v>
+        <v>-1.07677026705063</v>
       </c>
       <c r="B65" t="n">
-        <v>-0.903297387209629</v>
+        <v>-1.04534975077654</v>
       </c>
       <c r="C65" t="n">
-        <v>1.30664487290647</v>
+        <v>1.07782127132645</v>
       </c>
       <c r="D65" t="n">
-        <v>1.19812767083188</v>
+        <v>1.12366062153032</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.11093912146544</v>
+        <v>-0.919351813913155</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.61953721180108</v>
+        <v>-1.38926546035228</v>
       </c>
       <c r="G65" t="n">
-        <v>2.00526212159703</v>
+        <v>2.03401223782357</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>-1.0829851609965</v>
+        <v>-1.09738107005978</v>
       </c>
       <c r="B66" t="n">
-        <v>-0.936146749856713</v>
+        <v>-1.01753378435798</v>
       </c>
       <c r="C66" t="n">
-        <v>1.40469173120944</v>
+        <v>1.1469382731981</v>
       </c>
       <c r="D66" t="n">
-        <v>1.35983631354058</v>
+        <v>1.3398052195937</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.07694410853368</v>
+        <v>-1.20290651772949</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.47469601040682</v>
+        <v>-1.4756482892837</v>
       </c>
       <c r="G66" t="n">
-        <v>1.91870200800334</v>
+        <v>2.03993810738256</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>-0.950191541515184</v>
+        <v>-1.15884389963518</v>
       </c>
       <c r="B67" t="n">
-        <v>-1.11023416812903</v>
+        <v>-0.933376751622867</v>
       </c>
       <c r="C67" t="n">
-        <v>1.55545648982354</v>
+        <v>0.916312320393906</v>
       </c>
       <c r="D67" t="n">
-        <v>0.74683634117326</v>
+        <v>0.997871394321667</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.7204728477871</v>
+        <v>-0.733097548136567</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.42693434045993</v>
+        <v>-1.1817098172147</v>
       </c>
       <c r="G67" t="n">
-        <v>2.00099778076009</v>
+        <v>2.0317475543304</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>-0.965658989274149</v>
+        <v>-1.30114784314556</v>
       </c>
       <c r="B68" t="n">
-        <v>-1.14866803163876</v>
+        <v>-0.963664163757492</v>
       </c>
       <c r="C68" t="n">
-        <v>1.64445281063242</v>
+        <v>1.02308387604371</v>
       </c>
       <c r="D68" t="n">
-        <v>1.11817136947886</v>
+        <v>1.33220198181294</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.109989693892</v>
+        <v>-0.586398505721287</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.49741105300763</v>
+        <v>-1.07964224037528</v>
       </c>
       <c r="G68" t="n">
-        <v>1.99047209309419</v>
+        <v>1.95633956650211</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>-0.929866882759997</v>
+        <v>-1.10236747251154</v>
       </c>
       <c r="B69" t="n">
-        <v>-0.911702456735198</v>
+        <v>-0.838763528982972</v>
       </c>
       <c r="C69" t="n">
-        <v>1.39560057481565</v>
+        <v>0.754117922623912</v>
       </c>
       <c r="D69" t="n">
-        <v>0.9765187339127</v>
+        <v>1.28104919965779</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.06987492923112</v>
+        <v>-1.07618989141717</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.54069785227757</v>
+        <v>-1.49620233312283</v>
       </c>
       <c r="G69" t="n">
-        <v>2.05323458884846</v>
+        <v>1.99217574286138</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>-0.912853825329083</v>
+        <v>-1.0203164338092</v>
       </c>
       <c r="B70" t="n">
-        <v>-0.859432674830697</v>
+        <v>-1.074996490324</v>
       </c>
       <c r="C70" t="n">
-        <v>1.42189979630117</v>
+        <v>1.19040994674722</v>
       </c>
       <c r="D70" t="n">
-        <v>0.910488777205617</v>
+        <v>1.07447224450275</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.956782296166921</v>
+        <v>-0.955995112892962</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.55645173456046</v>
+        <v>-1.49573868298521</v>
       </c>
       <c r="G70" t="n">
-        <v>2.07773703527494</v>
+        <v>1.99045006050439</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>-1.28463026026961</v>
+        <v>-1.13731964006449</v>
       </c>
       <c r="B71" t="n">
-        <v>-1.07190197261867</v>
+        <v>-0.774008782126312</v>
       </c>
       <c r="C71" t="n">
-        <v>1.58007714682726</v>
+        <v>0.812351336267462</v>
       </c>
       <c r="D71" t="n">
-        <v>1.57898201378645</v>
+        <v>1.18958877981423</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.824537955007595</v>
+        <v>-0.89782703493316</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.60957006746087</v>
+        <v>-1.27249571157431</v>
       </c>
       <c r="G71" t="n">
-        <v>2.04276751675267</v>
+        <v>2.06084805084777</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>-0.839184372135565</v>
+        <v>-0.928570697841747</v>
       </c>
       <c r="B72" t="n">
-        <v>-0.977718910786383</v>
+        <v>-0.997469357132805</v>
       </c>
       <c r="C72" t="n">
-        <v>1.37705709123136</v>
+        <v>1.07449118011431</v>
       </c>
       <c r="D72" t="n">
-        <v>0.716384784461305</v>
+        <v>0.821338437494314</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.986802421483899</v>
+        <v>-1.08592927717035</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.56708285821407</v>
+        <v>-1.4779819735386</v>
       </c>
       <c r="G72" t="n">
-        <v>1.96025864936519</v>
+        <v>2.04120929002423</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>-1.10930446574517</v>
+        <v>-0.897942912236685</v>
       </c>
       <c r="B73" t="n">
-        <v>-0.904591013663405</v>
+        <v>-0.922542727404072</v>
       </c>
       <c r="C73" t="n">
-        <v>1.34059399102315</v>
+        <v>1.14155281793557</v>
       </c>
       <c r="D73" t="n">
-        <v>1.33136617703936</v>
+        <v>0.889704319371496</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.13508611796782</v>
+        <v>-1.22359661074333</v>
       </c>
       <c r="F73" t="n">
-        <v>-2.02094294907169</v>
+        <v>-1.5989141064987</v>
       </c>
       <c r="G73" t="n">
-        <v>2.09605287827917</v>
+        <v>2.06677115443223</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-0.895530397734618</v>
+        <v>-1.10526839226568</v>
       </c>
       <c r="B74" t="n">
-        <v>-1.0176559645209</v>
+        <v>-0.97551189402539</v>
       </c>
       <c r="C74" t="n">
-        <v>1.60300599801075</v>
+        <v>0.863856648639638</v>
       </c>
       <c r="D74" t="n">
-        <v>0.969093469337385</v>
+        <v>1.03095926297943</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.04138934568801</v>
+        <v>-0.870602910117687</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.63678306983661</v>
+        <v>-1.32260142035451</v>
       </c>
       <c r="G74" t="n">
-        <v>2.05827610513094</v>
+        <v>1.98676031571718</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>-0.977081335599801</v>
+        <v>-1.00668353115393</v>
       </c>
       <c r="B75" t="n">
-        <v>-1.11909353706432</v>
+        <v>-0.828047440206958</v>
       </c>
       <c r="C75" t="n">
-        <v>1.62150832928732</v>
+        <v>0.824361940957908</v>
       </c>
       <c r="D75" t="n">
-        <v>1.11580382144185</v>
+        <v>0.852891358818522</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.01231916948776</v>
+        <v>-0.974610550119714</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.46605405833392</v>
+        <v>-1.43272376978039</v>
       </c>
       <c r="G75" t="n">
-        <v>2.1355391771918</v>
+        <v>2.0065870519081</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>-1.24156233063044</v>
+        <v>-1.11019418505141</v>
       </c>
       <c r="B76" t="n">
-        <v>-1.19151214453575</v>
+        <v>-1.01744005251159</v>
       </c>
       <c r="C76" t="n">
-        <v>1.89252669827691</v>
+        <v>1.01606828636707</v>
       </c>
       <c r="D76" t="n">
-        <v>1.67298987532635</v>
+        <v>0.974451535443139</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.05822615705246</v>
+        <v>-1.11601019657551</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.8747441467373</v>
+        <v>-1.91560399438515</v>
       </c>
       <c r="G76" t="n">
-        <v>1.95030714797921</v>
+        <v>1.98026808974471</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>-1.06987533134247</v>
+        <v>-0.742680574452843</v>
       </c>
       <c r="B77" t="n">
-        <v>-0.929989015683403</v>
+        <v>-0.788159650096138</v>
       </c>
       <c r="C77" t="n">
-        <v>1.53787731751602</v>
+        <v>0.616778877121064</v>
       </c>
       <c r="D77" t="n">
-        <v>1.49666649256629</v>
+        <v>0.839244185344647</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.958631030302255</v>
+        <v>-1.6137492099849</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.48256688603028</v>
+        <v>-1.78366559643398</v>
       </c>
       <c r="G77" t="n">
-        <v>2.07516138404198</v>
+        <v>2.13836356881313</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>-0.9088472751771</v>
+        <v>-0.88937248678187</v>
       </c>
       <c r="B78" t="n">
-        <v>-0.999792872768263</v>
+        <v>-0.985403690477658</v>
       </c>
       <c r="C78" t="n">
-        <v>1.51649480577942</v>
+        <v>0.952654986009717</v>
       </c>
       <c r="D78" t="n">
-        <v>0.816196701500117</v>
+        <v>0.76346551346925</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.961705633925047</v>
+        <v>-1.27044167264919</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.5036985816862</v>
+        <v>-1.56429690937149</v>
       </c>
       <c r="G78" t="n">
-        <v>2.04521269374743</v>
+        <v>1.94033712672135</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>-0.999367502509532</v>
+        <v>-0.793406346538692</v>
       </c>
       <c r="B79" t="n">
-        <v>-0.862879808095791</v>
+        <v>-0.948642057035077</v>
       </c>
       <c r="C79" t="n">
-        <v>1.30852605626841</v>
+        <v>0.961473504981004</v>
       </c>
       <c r="D79" t="n">
-        <v>1.31567059965707</v>
+        <v>0.566863479691749</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.28764674981939</v>
+        <v>-1.12156793268225</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.68553060795224</v>
+        <v>-1.71009757695211</v>
       </c>
       <c r="G79" t="n">
-        <v>2.07462332296464</v>
+        <v>2.05902255681873</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>-1.02601972766661</v>
+        <v>-0.904512748182509</v>
       </c>
       <c r="B80" t="n">
-        <v>-1.08793221249823</v>
+        <v>-1.07611660640906</v>
       </c>
       <c r="C80" t="n">
-        <v>1.61327735926935</v>
+        <v>1.23226060187993</v>
       </c>
       <c r="D80" t="n">
-        <v>1.06480451144514</v>
+        <v>0.836660466553381</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.897129719867202</v>
+        <v>-1.16922141004117</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.30979785111943</v>
+        <v>-1.61992021059808</v>
       </c>
       <c r="G80" t="n">
-        <v>1.99607031073587</v>
+        <v>1.99811597388375</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>-0.993436740117433</v>
+        <v>-1.16280434501428</v>
       </c>
       <c r="B81" t="n">
-        <v>-0.7479450072994</v>
+        <v>-0.809916846197484</v>
       </c>
       <c r="C81" t="n">
-        <v>1.21590329623956</v>
+        <v>0.943518567892302</v>
       </c>
       <c r="D81" t="n">
-        <v>1.25263039972844</v>
+        <v>1.18596664710402</v>
       </c>
       <c r="E81" t="n">
-        <v>-1.02144659510099</v>
+        <v>-0.969357403725151</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.58931860774607</v>
+        <v>-1.23350853945299</v>
       </c>
       <c r="G81" t="n">
-        <v>2.07239457964542</v>
+        <v>2.08225566813738</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-1.13199932767996</v>
+        <v>-1.09118648588958</v>
       </c>
       <c r="B82" t="n">
-        <v>-0.822281033989186</v>
+        <v>-0.903169167469592</v>
       </c>
       <c r="C82" t="n">
-        <v>1.3798576043883</v>
+        <v>0.986177978049816</v>
       </c>
       <c r="D82" t="n">
-        <v>1.49634407087304</v>
+        <v>1.19973558867845</v>
       </c>
       <c r="E82" t="n">
-        <v>-1.01103336953338</v>
+        <v>-0.882760111617496</v>
       </c>
       <c r="F82" t="n">
-        <v>-1.33069890908461</v>
+        <v>-1.46165218332706</v>
       </c>
       <c r="G82" t="n">
-        <v>2.05121152636075</v>
+        <v>1.98104702631514</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>-1.16264058871005</v>
+        <v>-0.999084377889643</v>
       </c>
       <c r="B83" t="n">
-        <v>-1.12408527185418</v>
+        <v>-0.869527446821545</v>
       </c>
       <c r="C83" t="n">
-        <v>1.63584276988575</v>
+        <v>0.885209151109444</v>
       </c>
       <c r="D83" t="n">
-        <v>1.49669000612928</v>
+        <v>0.677701895016458</v>
       </c>
       <c r="E83" t="n">
-        <v>-1.03922772455325</v>
+        <v>-0.742965141655492</v>
       </c>
       <c r="F83" t="n">
-        <v>-2.09805800895194</v>
+        <v>-1.34012928157213</v>
       </c>
       <c r="G83" t="n">
-        <v>2.03415569236549</v>
+        <v>1.93233923448336</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>-1.24101338804241</v>
+        <v>-1.20334903049399</v>
       </c>
       <c r="B84" t="n">
-        <v>-1.07455940718186</v>
+        <v>-0.935869097979097</v>
       </c>
       <c r="C84" t="n">
-        <v>1.54249545428189</v>
+        <v>0.931833562408426</v>
       </c>
       <c r="D84" t="n">
-        <v>1.6367044006124</v>
+        <v>1.37226090881162</v>
       </c>
       <c r="E84" t="n">
-        <v>-1.06622603560037</v>
+        <v>-0.898884361063713</v>
       </c>
       <c r="F84" t="n">
-        <v>-2.14543139346766</v>
+        <v>-1.17761056090461</v>
       </c>
       <c r="G84" t="n">
-        <v>1.98592911767368</v>
+        <v>2.0579365031347</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>-0.977986127346549</v>
+        <v>-1.0715557147718</v>
       </c>
       <c r="B85" t="n">
-        <v>-0.804607683809907</v>
+        <v>-0.801380232708264</v>
       </c>
       <c r="C85" t="n">
-        <v>1.35206867845508</v>
+        <v>0.865501015767681</v>
       </c>
       <c r="D85" t="n">
-        <v>1.17407974868683</v>
+        <v>1.17486983221957</v>
       </c>
       <c r="E85" t="n">
-        <v>-1.20256518347584</v>
+        <v>-1.11323049430985</v>
       </c>
       <c r="F85" t="n">
-        <v>-1.61100048570672</v>
+        <v>-1.44153941775739</v>
       </c>
       <c r="G85" t="n">
-        <v>2.15203296535943</v>
+        <v>2.01732691289169</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>-0.869014991876794</v>
+        <v>-1.06769813270597</v>
       </c>
       <c r="B86" t="n">
-        <v>-1.09719232831394</v>
+        <v>-0.953466732611892</v>
       </c>
       <c r="C86" t="n">
-        <v>1.51807146508259</v>
+        <v>0.927094571528285</v>
       </c>
       <c r="D86" t="n">
-        <v>1.04291669753995</v>
+        <v>1.20318523614064</v>
       </c>
       <c r="E86" t="n">
-        <v>-1.12643946940173</v>
+        <v>-1.02569710248474</v>
       </c>
       <c r="F86" t="n">
-        <v>-1.55274146068447</v>
+        <v>-1.58678074030049</v>
       </c>
       <c r="G86" t="n">
-        <v>2.04949246601264</v>
+        <v>2.03004542368618</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>-0.834430444617173</v>
+        <v>-0.922113042273111</v>
       </c>
       <c r="B87" t="n">
-        <v>-1.01593247205625</v>
+        <v>-0.797749164479032</v>
       </c>
       <c r="C87" t="n">
-        <v>1.46378141075736</v>
+        <v>0.8982976511881</v>
       </c>
       <c r="D87" t="n">
-        <v>0.89659254082136</v>
+        <v>0.780585521012608</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.97877250504972</v>
+        <v>-1.10664625821818</v>
       </c>
       <c r="F87" t="n">
-        <v>-1.71030709674763</v>
+        <v>-1.56725874962113</v>
       </c>
       <c r="G87" t="n">
-        <v>2.02701680696903</v>
+        <v>2.06428776128823</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>-0.97844224990106</v>
+        <v>-0.949223517652763</v>
       </c>
       <c r="B88" t="n">
-        <v>-1.04202826641223</v>
+        <v>-0.91487568019622</v>
       </c>
       <c r="C88" t="n">
-        <v>1.56716600544806</v>
+        <v>0.950438345618264</v>
       </c>
       <c r="D88" t="n">
-        <v>1.10714174723247</v>
+        <v>0.95313043585705</v>
       </c>
       <c r="E88" t="n">
-        <v>-1.24096385286792</v>
+        <v>-1.08076366436699</v>
       </c>
       <c r="F88" t="n">
-        <v>-2.27771954338427</v>
+        <v>-1.50986684961796</v>
       </c>
       <c r="G88" t="n">
-        <v>1.95269181653962</v>
+        <v>2.06649266012863</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>-1.08464497086431</v>
+        <v>-0.865969001189428</v>
       </c>
       <c r="B89" t="n">
-        <v>-0.996450848885902</v>
+        <v>-0.906885814944787</v>
       </c>
       <c r="C89" t="n">
-        <v>1.62117804649603</v>
+        <v>0.999173629476152</v>
       </c>
       <c r="D89" t="n">
-        <v>1.39585175022579</v>
+        <v>0.830060339876895</v>
       </c>
       <c r="E89" t="n">
-        <v>-1.17865666639227</v>
+        <v>-1.20188813687473</v>
       </c>
       <c r="F89" t="n">
-        <v>-2.18562288982288</v>
+        <v>-1.61742173725443</v>
       </c>
       <c r="G89" t="n">
-        <v>2.11667120967146</v>
+        <v>1.90071006250355</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>-1.13652442269678</v>
+        <v>-1.12793153308343</v>
       </c>
       <c r="B90" t="n">
-        <v>-1.0071036656848</v>
+        <v>-0.961507914561902</v>
       </c>
       <c r="C90" t="n">
-        <v>1.65970051300653</v>
+        <v>0.930461796076691</v>
       </c>
       <c r="D90" t="n">
-        <v>1.40510504674269</v>
+        <v>1.18520658189187</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.978747483027767</v>
+        <v>-0.963192868118991</v>
       </c>
       <c r="F90" t="n">
-        <v>-2.06656439982953</v>
+        <v>-1.30700131636688</v>
       </c>
       <c r="G90" t="n">
-        <v>2.08802824399031</v>
+        <v>2.05446543051251</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>-1.08269276192844</v>
+        <v>-1.07016846225958</v>
       </c>
       <c r="B91" t="n">
-        <v>-1.00054136874099</v>
+        <v>-0.872669233020867</v>
       </c>
       <c r="C91" t="n">
-        <v>1.64617508339218</v>
+        <v>0.956229968453185</v>
       </c>
       <c r="D91" t="n">
-        <v>1.36427321497915</v>
+        <v>0.999613906067811</v>
       </c>
       <c r="E91" t="n">
-        <v>-1.02272231821027</v>
+        <v>-1.06671178157149</v>
       </c>
       <c r="F91" t="n">
-        <v>-1.49534834367567</v>
+        <v>-1.40726130675294</v>
       </c>
       <c r="G91" t="n">
-        <v>2.05269134754862</v>
+        <v>1.97203387415957</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>-1.20546003309368</v>
+        <v>-0.930540115932333</v>
       </c>
       <c r="B92" t="n">
-        <v>-1.10975375852184</v>
+        <v>-0.827619105742464</v>
       </c>
       <c r="C92" t="n">
-        <v>1.56538075342983</v>
+        <v>0.754158235792045</v>
       </c>
       <c r="D92" t="n">
-        <v>1.58757762911247</v>
+        <v>0.962520010737686</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.778184254481483</v>
+        <v>-1.01294110668973</v>
       </c>
       <c r="F92" t="n">
-        <v>-1.22205665474696</v>
+        <v>-1.59528703932014</v>
       </c>
       <c r="G92" t="n">
-        <v>2.02645842115248</v>
+        <v>1.9997912447134</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-1.06261288907061</v>
+        <v>-0.92065988769297</v>
       </c>
       <c r="B93" t="n">
-        <v>-0.975240857331017</v>
+        <v>-0.95238518190634</v>
       </c>
       <c r="C93" t="n">
-        <v>1.52883292078229</v>
+        <v>1.04909216760776</v>
       </c>
       <c r="D93" t="n">
-        <v>1.26354008510947</v>
+        <v>0.901021540256087</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.763649576883253</v>
+        <v>-1.18028696616999</v>
       </c>
       <c r="F93" t="n">
-        <v>-1.26671331915968</v>
+        <v>-1.61679928791027</v>
       </c>
       <c r="G93" t="n">
-        <v>2.15407351518425</v>
+        <v>2.01391965463516</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-1.16749928126451</v>
+        <v>-1.09819112852086</v>
       </c>
       <c r="B94" t="n">
-        <v>-1.10658538265874</v>
+        <v>-0.932351911369839</v>
       </c>
       <c r="C94" t="n">
-        <v>1.6722259156567</v>
+        <v>0.887994804145151</v>
       </c>
       <c r="D94" t="n">
-        <v>1.46938657942517</v>
+        <v>0.975831703357794</v>
       </c>
       <c r="E94" t="n">
-        <v>-1.00861648960273</v>
+        <v>-0.851578968734935</v>
       </c>
       <c r="F94" t="n">
-        <v>-1.33231893608315</v>
+        <v>-1.22878995574248</v>
       </c>
       <c r="G94" t="n">
-        <v>1.97519986927273</v>
+        <v>2.01123807403008</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>-0.892916393104957</v>
+        <v>-1.00642562062733</v>
       </c>
       <c r="B95" t="n">
-        <v>-0.9175788181404</v>
+        <v>-0.948158936385309</v>
       </c>
       <c r="C95" t="n">
-        <v>1.3213397605207</v>
+        <v>0.939771519378538</v>
       </c>
       <c r="D95" t="n">
-        <v>1.02027294576708</v>
+        <v>0.9642416812617</v>
       </c>
       <c r="E95" t="n">
-        <v>-1.10475957569659</v>
+        <v>-1.07471913059663</v>
       </c>
       <c r="F95" t="n">
-        <v>-1.65390744276806</v>
+        <v>-1.43937615384733</v>
       </c>
       <c r="G95" t="n">
-        <v>1.99265328128796</v>
+        <v>1.93053726826469</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-0.991212092962412</v>
+        <v>-1.05954651449478</v>
       </c>
       <c r="B96" t="n">
-        <v>-0.912041563264977</v>
+        <v>-1.00017459618782</v>
       </c>
       <c r="C96" t="n">
-        <v>1.50077859438519</v>
+        <v>1.02479814649399</v>
       </c>
       <c r="D96" t="n">
-        <v>1.0583400344151</v>
+        <v>1.09315980184523</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.963990433633761</v>
+        <v>-1.27918194260463</v>
       </c>
       <c r="F96" t="n">
-        <v>-1.40172572696735</v>
+        <v>-1.49104369207313</v>
       </c>
       <c r="G96" t="n">
-        <v>2.11202190761633</v>
+        <v>2.02113353929789</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-1.03456051384075</v>
+        <v>-0.864139270173111</v>
       </c>
       <c r="B97" t="n">
-        <v>-1.02332986165971</v>
+        <v>-1.1029450742674</v>
       </c>
       <c r="C97" t="n">
-        <v>1.43414905548161</v>
+        <v>1.15550119670441</v>
       </c>
       <c r="D97" t="n">
-        <v>1.27517227803309</v>
+        <v>0.857410949659197</v>
       </c>
       <c r="E97" t="n">
-        <v>-1.02048346224555</v>
+        <v>-1.48179687038523</v>
       </c>
       <c r="F97" t="n">
-        <v>-1.45946113057365</v>
+        <v>-1.70527982944588</v>
       </c>
       <c r="G97" t="n">
-        <v>1.96312513830463</v>
+        <v>1.99783987022409</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>-1.03554179453586</v>
+        <v>-1.22977464419162</v>
       </c>
       <c r="B98" t="n">
-        <v>-1.10891752847568</v>
+        <v>-0.957199374001675</v>
       </c>
       <c r="C98" t="n">
-        <v>1.70599358970018</v>
+        <v>0.957851953216462</v>
       </c>
       <c r="D98" t="n">
-        <v>1.03330844423293</v>
+        <v>1.31961929764264</v>
       </c>
       <c r="E98" t="n">
-        <v>-1.025675144844</v>
+        <v>-0.849518470412638</v>
       </c>
       <c r="F98" t="n">
-        <v>-2.0109667543425</v>
+        <v>-1.22336211107541</v>
       </c>
       <c r="G98" t="n">
-        <v>2.10857158401971</v>
+        <v>2.00457728709694</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>-1.09667140536256</v>
+        <v>-0.976968277568095</v>
       </c>
       <c r="B99" t="n">
-        <v>-0.913883075593587</v>
+        <v>-0.938999221340461</v>
       </c>
       <c r="C99" t="n">
-        <v>1.4279667189584</v>
+        <v>0.976227208626362</v>
       </c>
       <c r="D99" t="n">
-        <v>1.19671207931229</v>
+        <v>1.01449164969441</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.8423986906534</v>
+        <v>-1.15708993882632</v>
       </c>
       <c r="F99" t="n">
-        <v>-1.24461136116162</v>
+        <v>-1.47784839386022</v>
       </c>
       <c r="G99" t="n">
-        <v>2.12203640487572</v>
+        <v>2.01699114968708</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-0.994740745255782</v>
+        <v>-0.897549911672589</v>
       </c>
       <c r="B100" t="n">
-        <v>-0.979622122146467</v>
+        <v>-0.819736256446329</v>
       </c>
       <c r="C100" t="n">
-        <v>1.49595579325483</v>
+        <v>0.931656906336828</v>
       </c>
       <c r="D100" t="n">
-        <v>1.1369284134162</v>
+        <v>0.865548859403445</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.85372679225341</v>
+        <v>-1.27903368656317</v>
       </c>
       <c r="F100" t="n">
-        <v>-1.40922141787844</v>
+        <v>-1.56996957571557</v>
       </c>
       <c r="G100" t="n">
-        <v>2.11435728165533</v>
+        <v>2.09878510237119</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>-0.923632869803267</v>
+        <v>-0.884920850418454</v>
       </c>
       <c r="B101" t="n">
-        <v>-0.900431662648184</v>
+        <v>-0.983709714399082</v>
       </c>
       <c r="C101" t="n">
-        <v>1.2979838874785</v>
+        <v>0.987459325257499</v>
       </c>
       <c r="D101" t="n">
-        <v>1.04809960318823</v>
+        <v>0.785747385636146</v>
       </c>
       <c r="E101" t="n">
-        <v>-1.05743269469634</v>
+        <v>-1.53490293164597</v>
       </c>
       <c r="F101" t="n">
-        <v>-1.58899881022717</v>
+        <v>-1.64477021525066</v>
       </c>
       <c r="G101" t="n">
-        <v>2.02499378468551</v>
+        <v>1.93634954345252</v>
       </c>
     </row>
   </sheetData>
@@ -3146,826 +3149,826 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0596192593259898</v>
+        <v>8.70326733939048</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0271314059251377</v>
+        <v>0.357000995120166</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.708302989147914</v>
+        <v>3.93585795614982</v>
       </c>
       <c r="B3" t="n">
-        <v>0.155427066414209</v>
+        <v>0.296771155736808</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5.44999734375234</v>
+        <v>1.37339599262258</v>
       </c>
       <c r="B4" t="n">
-        <v>0.335005081373055</v>
+        <v>0.240138766658334</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1.20605369907054</v>
+        <v>0.0951536760549124</v>
       </c>
       <c r="B5" t="n">
-        <v>0.231195553081322</v>
+        <v>0.0479793835370482</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.158502099019901</v>
+        <v>2.33082108110793</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0628852974782194</v>
+        <v>0.26994340638193</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>15.5896854682464</v>
+        <v>0.456764473850029</v>
       </c>
       <c r="B7" t="n">
-        <v>0.412101748326758</v>
+        <v>0.125948712250684</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7.42168042756523</v>
+        <v>2.82079132196889</v>
       </c>
       <c r="B8" t="n">
-        <v>0.359208985179507</v>
+        <v>0.283248475781913</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1.4974407728584</v>
+        <v>2.20121980891325</v>
       </c>
       <c r="B9" t="n">
-        <v>0.234968158440881</v>
+        <v>0.254440582050122</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2.88070450843112</v>
+        <v>0.603377836966091</v>
       </c>
       <c r="B10" t="n">
-        <v>0.286607708428699</v>
+        <v>0.171213263057214</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.207815145267831</v>
+        <v>1.57995430345173</v>
       </c>
       <c r="B11" t="n">
-        <v>0.276024331793057</v>
+        <v>0.237264448079415</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1.08772426138542</v>
+        <v>0.385894694605255</v>
       </c>
       <c r="B12" t="n">
-        <v>0.202178119031814</v>
+        <v>0.357538044899489</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7.06799811340371</v>
+        <v>0.16867202687518</v>
       </c>
       <c r="B13" t="n">
-        <v>0.341450403514004</v>
+        <v>0.135473913765109</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.90187309011596</v>
+        <v>5.98597430312206</v>
       </c>
       <c r="B14" t="n">
-        <v>0.167847406363938</v>
+        <v>0.356703415645332</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.507274409378703</v>
+        <v>3.4045553913907</v>
       </c>
       <c r="B15" t="n">
-        <v>0.403371092172145</v>
+        <v>0.302425930295608</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3.7678007300856</v>
+        <v>9.96730912051869</v>
       </c>
       <c r="B16" t="n">
-        <v>0.317989731738547</v>
+        <v>0.392340380136243</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.114563666007844</v>
+        <v>1.18014889203969</v>
       </c>
       <c r="B17" t="n">
-        <v>0.223661090273804</v>
+        <v>0.235410960369784</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>30.0145510291435</v>
+        <v>8.34723785097956</v>
       </c>
       <c r="B18" t="n">
-        <v>0.447892261838237</v>
+        <v>0.359699485893168</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.138452831326717</v>
+        <v>4.51889757235943</v>
       </c>
       <c r="B19" t="n">
-        <v>0.382393135612565</v>
+        <v>0.302244375437225</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1.76689137021012</v>
+        <v>0.249761362678412</v>
       </c>
       <c r="B20" t="n">
-        <v>0.219504865549174</v>
+        <v>0.215359326838998</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2.4919686650374</v>
+        <v>2.0258604452233</v>
       </c>
       <c r="B21" t="n">
-        <v>0.281174297679312</v>
+        <v>0.270390699832576</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>7.37954529314987</v>
+        <v>0.94271425063379</v>
       </c>
       <c r="B22" t="n">
-        <v>0.336775899723505</v>
+        <v>0.176772990038675</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2.80933610498507</v>
+        <v>1.24427285216529</v>
       </c>
       <c r="B23" t="n">
-        <v>0.573806898273289</v>
+        <v>0.205893190124784</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2.45521554385313</v>
+        <v>0.328030381508205</v>
       </c>
       <c r="B24" t="n">
-        <v>0.29618641053006</v>
+        <v>0.105482977753593</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1.10274630580967</v>
+        <v>0.302161964094064</v>
       </c>
       <c r="B25" t="n">
-        <v>0.253794874255986</v>
+        <v>0.343498622878893</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.13639376032134</v>
+        <v>3.43886823305443</v>
       </c>
       <c r="B26" t="n">
-        <v>0.294401646841427</v>
+        <v>0.460333175470258</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.70176399068307</v>
+        <v>0.336077825729086</v>
       </c>
       <c r="B27" t="n">
-        <v>0.157625540680295</v>
+        <v>0.103091031336971</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>7.54244273779606</v>
+        <v>3.74141941564461</v>
       </c>
       <c r="B28" t="n">
-        <v>0.371957264095215</v>
+        <v>0.349980836883313</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.352666804133878</v>
+        <v>1.9336957590125</v>
       </c>
       <c r="B29" t="n">
-        <v>0.154767450003738</v>
+        <v>0.267377182899253</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.0690989158610908</v>
+        <v>3.03049691554982</v>
       </c>
       <c r="B30" t="n">
-        <v>0.0257610212412449</v>
+        <v>0.297085790284997</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4.23135619904405</v>
+        <v>3.64836259922193</v>
       </c>
       <c r="B31" t="n">
-        <v>0.306081125525889</v>
+        <v>0.290196619871607</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>14.4348071090554</v>
+        <v>1.64371314025941</v>
       </c>
       <c r="B32" t="n">
-        <v>0.411193809950029</v>
+        <v>0.210830707286924</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.0915375293910116</v>
+        <v>1.31168267936024</v>
       </c>
       <c r="B33" t="n">
-        <v>0.0738223789761549</v>
+        <v>0.215348438112101</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.23576125346738</v>
+        <v>2.73105219897087</v>
       </c>
       <c r="B34" t="n">
-        <v>0.090352681252901</v>
+        <v>0.283490113059276</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>7.09323831880773</v>
+        <v>6.13667491348689</v>
       </c>
       <c r="B35" t="n">
-        <v>0.368143654682767</v>
+        <v>0.33735207464601</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1.12829862021867</v>
+        <v>12.5818321925346</v>
       </c>
       <c r="B36" t="n">
-        <v>0.223201738783637</v>
+        <v>0.413397526208639</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.366365203806304</v>
+        <v>37.2366810796032</v>
       </c>
       <c r="B37" t="n">
-        <v>0.10262233563433</v>
+        <v>0.467023447626878</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.967798635217886</v>
+        <v>6.36238563168228</v>
       </c>
       <c r="B38" t="n">
-        <v>0.199448797953819</v>
+        <v>0.353101382782661</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1.14320169037949</v>
+        <v>1.87403104544374</v>
       </c>
       <c r="B39" t="n">
-        <v>0.209956095742792</v>
+        <v>0.43382477038944</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>9.81025363618581</v>
+        <v>2.7130620369449</v>
       </c>
       <c r="B40" t="n">
-        <v>0.409859794437822</v>
+        <v>0.273688680585695</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.348668615467366</v>
+        <v>1.3469533060944</v>
       </c>
       <c r="B41" t="n">
-        <v>0.121900406428932</v>
+        <v>0.224417297553744</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2.33365672247708</v>
+        <v>0.309522134975798</v>
       </c>
       <c r="B42" t="n">
-        <v>0.241851457334316</v>
+        <v>0.0993404228705436</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>3.57416041220801</v>
+        <v>5.31290795739033</v>
       </c>
       <c r="B43" t="n">
-        <v>0.31036918676043</v>
+        <v>0.324854469554392</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.380477578713571</v>
+        <v>1.75132974713312</v>
       </c>
       <c r="B44" t="n">
-        <v>0.292146314446943</v>
+        <v>0.240634130291105</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>6.23656046984246</v>
+        <v>0.741447655916005</v>
       </c>
       <c r="B45" t="n">
-        <v>0.370639822240461</v>
+        <v>0.198885725769247</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.503487381180235</v>
+        <v>33.3243289992157</v>
       </c>
       <c r="B46" t="n">
-        <v>0.432518899458294</v>
+        <v>0.469596022091656</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1.87014289486424</v>
+        <v>0.816918226055383</v>
       </c>
       <c r="B47" t="n">
-        <v>0.232513512485421</v>
+        <v>0.178264936320801</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.408914553291783</v>
+        <v>1.0610828602602</v>
       </c>
       <c r="B48" t="n">
-        <v>0.140830905354741</v>
+        <v>0.21312617866195</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1.27976068701559</v>
+        <v>0.100540954336845</v>
       </c>
       <c r="B49" t="n">
-        <v>0.503675811132557</v>
+        <v>0.0534926558149433</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>8.80110128172448</v>
+        <v>2.1072835717133</v>
       </c>
       <c r="B50" t="n">
-        <v>0.370012941607456</v>
+        <v>0.256074428927963</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2.2758561291176</v>
+        <v>0.496676116597696</v>
       </c>
       <c r="B51" t="n">
-        <v>0.258973317548465</v>
+        <v>0.131698765481773</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.272555494621166</v>
+        <v>2.23285310556634</v>
       </c>
       <c r="B52" t="n">
-        <v>0.3539251143648</v>
+        <v>0.252064291933462</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.331309216481517</v>
+        <v>2.41822135379072</v>
       </c>
       <c r="B53" t="n">
-        <v>0.125748477859036</v>
+        <v>0.274801559295034</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>6.24753100594146</v>
+        <v>0.235396049638019</v>
       </c>
       <c r="B54" t="n">
-        <v>0.331854475855834</v>
+        <v>0.0937096834346682</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>3.43693493515058</v>
+        <v>15.9773486150855</v>
       </c>
       <c r="B55" t="n">
-        <v>0.498980042614997</v>
+        <v>0.391968149391737</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1.57037632785732</v>
+        <v>17.4458544360745</v>
       </c>
       <c r="B56" t="n">
-        <v>0.228848973852277</v>
+        <v>0.404745995740246</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2.69672027225424</v>
+        <v>0.740085115287504</v>
       </c>
       <c r="B57" t="n">
-        <v>0.289316866084769</v>
+        <v>0.146817210795006</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.747915856987319</v>
+        <v>5.07629521513374</v>
       </c>
       <c r="B58" t="n">
-        <v>0.202561355156769</v>
+        <v>0.315935215726088</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1.81654520879574</v>
+        <v>0.924875854952649</v>
       </c>
       <c r="B59" t="n">
-        <v>0.25855452497687</v>
+        <v>0.186298032008839</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.600231732091082</v>
+        <v>1.07023139416096</v>
       </c>
       <c r="B60" t="n">
-        <v>0.418994149879736</v>
+        <v>0.207733623816845</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.0761949316937058</v>
+        <v>0.0884818354831401</v>
       </c>
       <c r="B61" t="n">
-        <v>0.388274517265751</v>
+        <v>0.0338926650009947</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.230013018226599</v>
+        <v>1.08608800036426</v>
       </c>
       <c r="B62" t="n">
-        <v>0.301880003024771</v>
+        <v>0.186017791925647</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1.77770526191283</v>
+        <v>14.7147368328648</v>
       </c>
       <c r="B63" t="n">
-        <v>0.462589967656145</v>
+        <v>0.403548422584124</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.216429631577108</v>
+        <v>1.15264380561141</v>
       </c>
       <c r="B64" t="n">
-        <v>0.351264994984789</v>
+        <v>0.203163447770366</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>10.8444749824525</v>
+        <v>1.74635821528901</v>
       </c>
       <c r="B65" t="n">
-        <v>0.376991881084836</v>
+        <v>0.227777189693408</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2.37759602919448</v>
+        <v>2.63342420454195</v>
       </c>
       <c r="B66" t="n">
-        <v>0.271063964497185</v>
+        <v>0.275251153641061</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.967947210228205</v>
+        <v>0.056580419592176</v>
       </c>
       <c r="B67" t="n">
-        <v>0.216383816331644</v>
+        <v>0.0345627878121281</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2.70836246101679</v>
+        <v>0.161654973193437</v>
       </c>
       <c r="B68" t="n">
-        <v>0.283881451199986</v>
+        <v>0.137061965025662</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2.80491404841741</v>
+        <v>2.98275855159121</v>
       </c>
       <c r="B69" t="n">
-        <v>0.307827066609041</v>
+        <v>0.283492943487967</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>4.63389914850926</v>
+        <v>2.80093617776881</v>
       </c>
       <c r="B70" t="n">
-        <v>0.322543051143072</v>
+        <v>0.287318210645275</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.210703619697414</v>
+        <v>0.307568380440071</v>
       </c>
       <c r="B71" t="n">
-        <v>0.188930371225488</v>
+        <v>0.106686047283018</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>3.81740982970624</v>
+        <v>1.71192716879467</v>
       </c>
       <c r="B72" t="n">
-        <v>0.328050962347292</v>
+        <v>0.266989098526183</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.304101621256203</v>
+        <v>7.24445103208302</v>
       </c>
       <c r="B73" t="n">
-        <v>0.319465313317191</v>
+        <v>0.359779677992582</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>5.82867100955016</v>
+        <v>0.532903908098366</v>
       </c>
       <c r="B74" t="n">
-        <v>0.367464061689329</v>
+        <v>0.142299575593406</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2.43327128757713</v>
+        <v>1.39267964016303</v>
       </c>
       <c r="B75" t="n">
-        <v>0.270264379021752</v>
+        <v>0.236206969450781</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.240309923696338</v>
+        <v>0.313620011933332</v>
       </c>
       <c r="B76" t="n">
-        <v>0.251992471214822</v>
+        <v>0.294536453242097</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1.45554510493293</v>
+        <v>48.8132703353112</v>
       </c>
       <c r="B77" t="n">
-        <v>0.264625490892345</v>
+        <v>0.488943259454918</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>3.70094271660306</v>
+        <v>6.90219471130911</v>
       </c>
       <c r="B78" t="n">
-        <v>0.290856654591968</v>
+        <v>0.346494705905606</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>11.4833441126817</v>
+        <v>10.7409705426427</v>
       </c>
       <c r="B79" t="n">
-        <v>0.39883361607725</v>
+        <v>0.416846028816646</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.521165218517762</v>
+        <v>10.2788707911567</v>
       </c>
       <c r="B80" t="n">
-        <v>0.140269811860789</v>
+        <v>0.37449737685191</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>7.15855691076998</v>
+        <v>0.293437118040046</v>
       </c>
       <c r="B81" t="n">
-        <v>0.34979260940131</v>
+        <v>0.0849482984541085</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>0.234046281668295</v>
+        <v>2.28554564558046</v>
       </c>
       <c r="B82" t="n">
-        <v>0.135327867114409</v>
+        <v>0.263381772350454</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0.132224045583052</v>
+        <v>1.0959529765365</v>
       </c>
       <c r="B83" t="n">
-        <v>0.385835330094731</v>
+        <v>0.190230539987786</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0.172453666195922</v>
+        <v>0.161862255896371</v>
       </c>
       <c r="B84" t="n">
-        <v>0.330518002662413</v>
+        <v>0.0495371565631787</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>7.55718407112429</v>
+        <v>1.00855925353729</v>
       </c>
       <c r="B85" t="n">
-        <v>0.363789852178877</v>
+        <v>0.233762250405912</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>7.4020589360212</v>
+        <v>4.08298921862025</v>
       </c>
       <c r="B86" t="n">
-        <v>0.333383067868518</v>
+        <v>0.337839547265523</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>15.4884332388141</v>
+        <v>6.3079844922155</v>
       </c>
       <c r="B87" t="n">
-        <v>0.419908166691918</v>
+        <v>0.334360746877095</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>0.807235690598636</v>
+        <v>4.36458270171303</v>
       </c>
       <c r="B88" t="n">
-        <v>0.443915146913967</v>
+        <v>0.304941210112856</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0.25254920945443</v>
+        <v>17.3557658854129</v>
       </c>
       <c r="B89" t="n">
-        <v>0.418780992941882</v>
+        <v>0.40118608101799</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>0.195276763393811</v>
+        <v>0.53140276092607</v>
       </c>
       <c r="B90" t="n">
-        <v>0.301247417250516</v>
+        <v>0.142008648902514</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1.94837893507747</v>
+        <v>1.53014783705531</v>
       </c>
       <c r="B91" t="n">
-        <v>0.271096199515575</v>
+        <v>0.21463331925503</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.114358419924046</v>
+        <v>10.9719036884066</v>
       </c>
       <c r="B92" t="n">
-        <v>0.0494061081695467</v>
+        <v>0.363250923890562</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>0.369733108004913</v>
+        <v>12.6012850019334</v>
       </c>
       <c r="B93" t="n">
-        <v>0.111661340791864</v>
+        <v>0.382770286486476</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0.638701285038479</v>
+        <v>0.23801064646464</v>
       </c>
       <c r="B94" t="n">
-        <v>0.158617816627703</v>
+        <v>0.0726494110005389</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>9.37834126619746</v>
+        <v>2.50605469739021</v>
       </c>
       <c r="B95" t="n">
-        <v>0.382665233092963</v>
+        <v>0.2578518138119</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1.52388402047061</v>
+        <v>3.01858422077432</v>
       </c>
       <c r="B96" t="n">
-        <v>0.223263396340537</v>
+        <v>0.28608358488144</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1.68861402677371</v>
+        <v>18.9207205919728</v>
       </c>
       <c r="B97" t="n">
-        <v>0.254773624243047</v>
+        <v>0.429493782443979</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0.203666695028091</v>
+        <v>0.252569034723823</v>
       </c>
       <c r="B98" t="n">
-        <v>0.287298063481402</v>
+        <v>0.0739371114033695</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>0.193989355034731</v>
+        <v>2.05744890266564</v>
       </c>
       <c r="B99" t="n">
-        <v>0.0733148308080269</v>
+        <v>0.271885820015717</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1.73651549228831</v>
+        <v>7.1197209710411</v>
       </c>
       <c r="B100" t="n">
-        <v>0.231227031396508</v>
+        <v>0.342706562442253</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2.87045632282447</v>
+        <v>14.6890022610071</v>
       </c>
       <c r="B101" t="n">
-        <v>0.334356382667778</v>
+        <v>0.395254201859188</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B103" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>3.07523293214764</v>
+        <v>4.72417932934692</v>
       </c>
       <c r="B104" t="n">
-        <v>0.281756260405313</v>
+        <v>0.260018429156188</v>
       </c>
     </row>
   </sheetData>
@@ -3981,18 +3984,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46016.8802458861</v>
+        <v>46026.1795428</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
